--- a/pages/shp/uploads/22-07-2026 - 22-07-2026.xlsx
+++ b/pages/shp/uploads/22-07-2026 - 22-07-2026.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="324">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -347,481 +347,496 @@
     <t>FLAG PROPORSIONAL NETTO</t>
   </si>
   <si>
-    <t>000030NIW34520260722001162</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>000033NIW34520260722000030</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>160200</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>DW03</t>
+  </si>
+  <si>
+    <t>3204</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>AEJEA</t>
+  </si>
+  <si>
+    <t>IDTPP</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DN</t>
+  </si>
+  <si>
+    <t>BANDUNG</t>
+  </si>
+  <si>
+    <t>YUS YULIUS</t>
+  </si>
+  <si>
+    <t>MANAGER EXIM</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
   <si>
     <t>040300</t>
   </si>
   <si>
-    <t>050500</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>41</t>
+    <t>155264</t>
+  </si>
+  <si>
+    <t>000033NIW34520260722000029</t>
+  </si>
+  <si>
+    <t>TW</t>
+  </si>
+  <si>
+    <t>TWTPE</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>155260</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS TARIF</t>
+  </si>
+  <si>
+    <t>KODE JENIS PUNGUTAN</t>
+  </si>
+  <si>
+    <t>NILAI PUNGUTAN</t>
+  </si>
+  <si>
+    <t>NPWP BILLING</t>
+  </si>
+  <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>KODE AFILIASI</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>IDTPP</t>
-  </si>
-  <si>
-    <t>ECGYE</t>
-  </si>
-  <si>
-    <t>2026-07-28</t>
-  </si>
-  <si>
-    <t>2026-07-22</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>DN</t>
-  </si>
-  <si>
-    <t>BANDUNG</t>
-  </si>
-  <si>
-    <t>YUS YULIUS</t>
-  </si>
-  <si>
-    <t>MANAGER EXIM</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>EXW</t>
-  </si>
-  <si>
-    <t>450093</t>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO 289
+DESA SOLOKAN JERUK KECAMATAN SOLOKAN JERUK
+KABUPATEN BANDUNG</t>
+  </si>
+  <si>
+    <t>SUN AND SAND SPORTS LLC/1052284</t>
+  </si>
+  <si>
+    <t>PLOT S10812 JEBEL ALI FREE ZONE S
+DUBAI</t>
+  </si>
+  <si>
+    <t>0010720829058000000000</t>
+  </si>
+  <si>
+    <t>MAERSK LOGISTICS INDONESIA</t>
+  </si>
+  <si>
+    <t>GEDUNG INTERNATIONAL FINANCIAL CENTRE TOWER 2 LT 40-41 JL JENDERAL SUDIRMAN KAV 22-23 RT.000 RW.000, KARET, SETIABUDI, KOTA ADMINISTRASI JAKARTA SELATAN, DAERAH KHUSUS IBUKOTA JAKARTA</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>410/MK/WBC.08/2026</t>
+  </si>
+  <si>
+    <t>06-30-2026 00:00:00</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>BO CHUAN INDUSTRIAL CO LTD/1020713</t>
+  </si>
+  <si>
+    <t>14F-5, NO646, SEC 5 CHONGSIN RD
+SAN-CHONG DIST.
+NEW TAIPEI CITY 241, 241</t>
+  </si>
+  <si>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>TFKC26070065</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>920</t>
+  </si>
+  <si>
+    <t>16/MK/WBC.09/2026</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>TFKC26070062</t>
+  </si>
+  <si>
+    <t>KODE CARA ANGKUT</t>
+  </si>
+  <si>
+    <t>NAMA PENGANGKUT</t>
+  </si>
+  <si>
+    <t>NOMOR PENGANGKUT</t>
+  </si>
+  <si>
+    <t>KODE BENDERA</t>
+  </si>
+  <si>
+    <t>CALL SIGN</t>
+  </si>
+  <si>
+    <t>FLAG ANGKUT PLB</t>
+  </si>
+  <si>
+    <t>CARA PENGANGKUTAN LAINNYA</t>
+  </si>
+  <si>
+    <t>EVER ORIGIN</t>
+  </si>
+  <si>
+    <t>059 N</t>
+  </si>
+  <si>
+    <t>EVER BUILD</t>
+  </si>
+  <si>
+    <t>1201-087A</t>
+  </si>
+  <si>
+    <t>KODE KEMASAN</t>
+  </si>
+  <si>
+    <t>JUMLAH KEMASAN</t>
+  </si>
+  <si>
+    <t>MEREK</t>
+  </si>
+  <si>
+    <t>NOMOR SEGEL</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>COLUMBIA</t>
+  </si>
+  <si>
+    <t>NOMOR KONTINER</t>
+  </si>
+  <si>
+    <t>KODE UKURAN KONTAINER</t>
+  </si>
+  <si>
+    <t>KODE JENIS KONTAINER</t>
+  </si>
+  <si>
+    <t>KODE TIPE KONTAINER</t>
+  </si>
+  <si>
+    <t>SERI BARANG</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>KODE BARANG</t>
+  </si>
+  <si>
+    <t>URAIAN</t>
+  </si>
+  <si>
+    <t>TIPE</t>
+  </si>
+  <si>
+    <t>UKURAN</t>
+  </si>
+  <si>
+    <t>SPESIFIKASI LAIN</t>
+  </si>
+  <si>
+    <t>KODE SATUAN</t>
+  </si>
+  <si>
+    <t>JUMLAH SATUAN</t>
+  </si>
+  <si>
+    <t>KODE DOKUMEN ASAL</t>
+  </si>
+  <si>
+    <t>KODE KANTOR ASAL</t>
+  </si>
+  <si>
+    <t>NOMOR DAFTAR ASAL</t>
+  </si>
+  <si>
+    <t>TANGGAL DAFTAR ASAL</t>
+  </si>
+  <si>
+    <t>NOMOR AJU ASAL</t>
+  </si>
+  <si>
+    <t>SERI BARANG ASAL</t>
+  </si>
+  <si>
+    <t>SALDO AWAL</t>
+  </si>
+  <si>
+    <t>SALDO AKHIR</t>
+  </si>
+  <si>
+    <t>JUMLAH REALISASI</t>
+  </si>
+  <si>
+    <t>CIF RUPIAH</t>
+  </si>
+  <si>
+    <t>NILAI TAMBAH</t>
+  </si>
+  <si>
+    <t>DISKON</t>
+  </si>
+  <si>
+    <t>HARGA PENYERAHAN</t>
+  </si>
+  <si>
+    <t>HARGA PEROLEHAN</t>
+  </si>
+  <si>
+    <t>HARGA SATUAN</t>
+  </si>
+  <si>
+    <t>HARGA EKSPOR</t>
+  </si>
+  <si>
+    <t>HARGA PATOKAN</t>
+  </si>
+  <si>
+    <t>NILAI DANA SAWIT</t>
+  </si>
+  <si>
+    <t>NILAI DEVISA</t>
+  </si>
+  <si>
+    <t>PERSENTASE IMPOR</t>
+  </si>
+  <si>
+    <t>KODE ASAL BARANG</t>
+  </si>
+  <si>
+    <t>KODE GUNA BARANG</t>
+  </si>
+  <si>
+    <t>JATUH TEMPO ROYALTI</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI BARANG</t>
+  </si>
+  <si>
+    <t>KODE KONDISI BARANG</t>
+  </si>
+  <si>
+    <t>KODE NEGARA ASAL</t>
+  </si>
+  <si>
+    <t>KODE PERHITUNGAN</t>
+  </si>
+  <si>
+    <t>PERNYATAAN LARTAS</t>
+  </si>
+  <si>
+    <t>FLAG 4 TAHUN</t>
+  </si>
+  <si>
+    <t>SERI IZIN</t>
+  </si>
+  <si>
+    <t>TAHUN PEMBUATAN</t>
+  </si>
+  <si>
+    <t>KAPASITAS SILINDER</t>
+  </si>
+  <si>
+    <t>KODE BKC</t>
+  </si>
+  <si>
+    <t>KODE KOMODITI BKC</t>
+  </si>
+  <si>
+    <t>KODE SUB KOMODITI BKC</t>
+  </si>
+  <si>
+    <t>FLAG TIS</t>
+  </si>
+  <si>
+    <t>ISI PER KEMASAN</t>
+  </si>
+  <si>
+    <t>JUMLAH DILEKATKAN</t>
+  </si>
+  <si>
+    <t>JUMLAH PITA CUKAI</t>
+  </si>
+  <si>
+    <t>HJE CUKAI</t>
+  </si>
+  <si>
+    <t>TARIF CUKAI</t>
+  </si>
+  <si>
+    <t>METODE PENENTUAN NILAI</t>
+  </si>
+  <si>
+    <t>ALASAN METODE PENENTUAN NILAI</t>
+  </si>
+  <si>
+    <t>STATEMENT PERBEDAAN HARGA</t>
+  </si>
+  <si>
+    <t>61052010</t>
+  </si>
+  <si>
+    <t>CLB/0426/037</t>
+  </si>
+  <si>
+    <t>POLO SHIRT (UTILIZER™ POLO)
+PO NO : 4550374155
+STYLE : AM0126</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
-    <t>KODE FASILITAS TARIF</t>
-  </si>
-  <si>
-    <t>KODE JENIS PUNGUTAN</t>
-  </si>
-  <si>
-    <t>NILAI PUNGUTAN</t>
-  </si>
-  <si>
-    <t>NPWP BILLING</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>KODE AFILIASI</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>GRETEL ECUADOR S.A.S./1051141</t>
-  </si>
-  <si>
-    <t>AV. DE LOS SHYRIS N35-174.
-EDIFICIO RENAZZO PLAZZA,
-QUITO, 170135</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
-  </si>
-  <si>
-    <t>NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>0016022097046000000000</t>
-  </si>
-  <si>
-    <t>MASAJI KARGOSENTRA TAMA</t>
-  </si>
-  <si>
-    <t>JALAN RAYA CAKUNG NO.15 RT.004 RW.010, SEMPER TIMUR, CILINCING, KOTA ADMINISTRASI JAKARTA UTARA, DAERAH KHUSUS IBUKOTA JAKARTA</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>00000000000000000</t>
-  </si>
-  <si>
-    <t>FE NEW CENTURY INDUSTRY (SINGAPORE) PTE. LTD.</t>
-  </si>
-  <si>
-    <t>9 LITTLE ROAD
-SINGAPORE, 536985
-SINGAPORE</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>16/MK/WBC.09/2026</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>TFKC26070064</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>KODE CARA ANGKUT</t>
-  </si>
-  <si>
-    <t>NAMA PENGANGKUT</t>
-  </si>
-  <si>
-    <t>NOMOR PENGANGKUT</t>
-  </si>
-  <si>
-    <t>KODE BENDERA</t>
-  </si>
-  <si>
-    <t>CALL SIGN</t>
-  </si>
-  <si>
-    <t>FLAG ANGKUT PLB</t>
-  </si>
-  <si>
-    <t>CARA PENGANGKUTAN LAINNYA</t>
-  </si>
-  <si>
-    <t>BELAWAN</t>
-  </si>
-  <si>
-    <t>2607N</t>
-  </si>
-  <si>
-    <t>HK</t>
-  </si>
-  <si>
-    <t>KODE KEMASAN</t>
-  </si>
-  <si>
-    <t>JUMLAH KEMASAN</t>
-  </si>
-  <si>
-    <t>MEREK</t>
-  </si>
-  <si>
-    <t>NOMOR SEGEL</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>COLUMBIA</t>
-  </si>
-  <si>
-    <t>NOMOR KONTINER</t>
-  </si>
-  <si>
-    <t>KODE UKURAN KONTAINER</t>
-  </si>
-  <si>
-    <t>KODE JENIS KONTAINER</t>
-  </si>
-  <si>
-    <t>KODE TIPE KONTAINER</t>
-  </si>
-  <si>
-    <t>SERI BARANG</t>
-  </si>
-  <si>
-    <t>HS</t>
-  </si>
-  <si>
-    <t>KODE BARANG</t>
-  </si>
-  <si>
-    <t>URAIAN</t>
-  </si>
-  <si>
-    <t>TIPE</t>
-  </si>
-  <si>
-    <t>UKURAN</t>
-  </si>
-  <si>
-    <t>SPESIFIKASI LAIN</t>
-  </si>
-  <si>
-    <t>KODE SATUAN</t>
-  </si>
-  <si>
-    <t>JUMLAH SATUAN</t>
-  </si>
-  <si>
-    <t>KODE DOKUMEN ASAL</t>
-  </si>
-  <si>
-    <t>KODE KANTOR ASAL</t>
-  </si>
-  <si>
-    <t>NOMOR DAFTAR ASAL</t>
-  </si>
-  <si>
-    <t>TANGGAL DAFTAR ASAL</t>
-  </si>
-  <si>
-    <t>NOMOR AJU ASAL</t>
-  </si>
-  <si>
-    <t>SERI BARANG ASAL</t>
-  </si>
-  <si>
-    <t>SALDO AWAL</t>
-  </si>
-  <si>
-    <t>SALDO AKHIR</t>
-  </si>
-  <si>
-    <t>JUMLAH REALISASI</t>
-  </si>
-  <si>
-    <t>CIF RUPIAH</t>
-  </si>
-  <si>
-    <t>NILAI TAMBAH</t>
-  </si>
-  <si>
-    <t>DISKON</t>
-  </si>
-  <si>
-    <t>HARGA PENYERAHAN</t>
-  </si>
-  <si>
-    <t>HARGA PEROLEHAN</t>
-  </si>
-  <si>
-    <t>HARGA SATUAN</t>
-  </si>
-  <si>
-    <t>HARGA EKSPOR</t>
-  </si>
-  <si>
-    <t>HARGA PATOKAN</t>
-  </si>
-  <si>
-    <t>NILAI DANA SAWIT</t>
-  </si>
-  <si>
-    <t>NILAI DEVISA</t>
-  </si>
-  <si>
-    <t>PERSENTASE IMPOR</t>
-  </si>
-  <si>
-    <t>KODE ASAL BARANG</t>
-  </si>
-  <si>
-    <t>KODE GUNA BARANG</t>
-  </si>
-  <si>
-    <t>JATUH TEMPO ROYALTI</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI BARANG</t>
-  </si>
-  <si>
-    <t>KODE KONDISI BARANG</t>
-  </si>
-  <si>
-    <t>KODE NEGARA ASAL</t>
-  </si>
-  <si>
-    <t>KODE PERHITUNGAN</t>
-  </si>
-  <si>
-    <t>PERNYATAAN LARTAS</t>
-  </si>
-  <si>
-    <t>FLAG 4 TAHUN</t>
-  </si>
-  <si>
-    <t>SERI IZIN</t>
-  </si>
-  <si>
-    <t>TAHUN PEMBUATAN</t>
-  </si>
-  <si>
-    <t>KAPASITAS SILINDER</t>
-  </si>
-  <si>
-    <t>KODE BKC</t>
-  </si>
-  <si>
-    <t>KODE KOMODITI BKC</t>
-  </si>
-  <si>
-    <t>KODE SUB KOMODITI BKC</t>
-  </si>
-  <si>
-    <t>FLAG TIS</t>
-  </si>
-  <si>
-    <t>ISI PER KEMASAN</t>
-  </si>
-  <si>
-    <t>JUMLAH DILEKATKAN</t>
-  </si>
-  <si>
-    <t>JUMLAH PITA CUKAI</t>
-  </si>
-  <si>
-    <t>HJE CUKAI</t>
-  </si>
-  <si>
-    <t>TARIF CUKAI</t>
-  </si>
-  <si>
-    <t>METODE PENENTUAN NILAI</t>
-  </si>
-  <si>
-    <t>ALASAN METODE PENENTUAN NILAI</t>
-  </si>
-  <si>
-    <t>STATEMENT PERBEDAAN HARGA</t>
-  </si>
-  <si>
-    <t>61052010</t>
-  </si>
-  <si>
-    <t>CLB/0426/037</t>
-  </si>
-  <si>
-    <t>POLO SHIRT ( UTILIZER POLO)
-PO NO  : 4550360189
-STYLE  : AM0126</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>PCE</t>
-  </si>
-  <si>
-    <t>3204</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>POLO SHIRT ( UTILIZER POLO)
-PO NO  : 4550360297
-STYLE  : AM0126</t>
-  </si>
-  <si>
-    <t>POLO SHIRT ( UTILIZER POLO)
-PO NO  : 4550360296
-STYLE  : AM0126</t>
-  </si>
-  <si>
-    <t>POLO SHIRT ( UTILIZER POLO)
-PO NO  : 4550360367
-STYLE  : AM0126</t>
+    <t>CLB/0226/016</t>
+  </si>
+  <si>
+    <t>POLO SHIRT (UTILIZER™ POLO)
+PO NO : 4550374432
+STYLE : AX0126</t>
   </si>
   <si>
     <t>KODE PUNGUTAN</t>
@@ -983,10 +998,22 @@
     <t>TANGGAL RESPON</t>
   </si>
   <si>
-    <t>3015</t>
-  </si>
-  <si>
-    <t>450042/PM/KPU.1/2026</t>
+    <t>3303</t>
+  </si>
+  <si>
+    <t>153192/KBC.0802/2026</t>
+  </si>
+  <si>
+    <t>3304</t>
+  </si>
+  <si>
+    <t>159721/KBC.0802/2026</t>
+  </si>
+  <si>
+    <t>153188/KBC.0802/2026</t>
+  </si>
+  <si>
+    <t>159940/KBC.0802/2026</t>
   </si>
 </sst>
 </file>
@@ -1479,65 +1506,65 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>107</v>
       </c>
-      <c r="G2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P2" t="s">
         <v>108</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>110</v>
       </c>
       <c r="W2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE2" t="s">
         <v>111</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH2" t="s">
         <v>112</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AN2" t="s">
         <v>113</v>
       </c>
       <c r="AO2" t="s">
         <v>114</v>
       </c>
       <c r="AR2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW2" t="s">
         <v>115</v>
       </c>
-      <c r="AS2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" t="s">
+      <c r="AX2" t="s">
         <v>116</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BE2" t="s">
         <v>117</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>118</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>119</v>
       </c>
       <c r="BK2" t="n">
         <v>0.0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.0</v>
+        <v>365.28</v>
       </c>
       <c r="BN2" t="n">
-        <v>1696.08</v>
+        <v>71.04</v>
       </c>
       <c r="BO2" t="n">
         <v>0.0</v>
@@ -1546,7 +1573,7 @@
         <v>0.0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8721.06</v>
+        <v>365.28</v>
       </c>
       <c r="BR2" t="n">
         <v>0.0</v>
@@ -1573,49 +1600,186 @@
         <v>0.0</v>
       </c>
       <c r="CB2" t="n">
-        <v>337.44</v>
+        <v>16.09</v>
       </c>
       <c r="CC2" t="n">
-        <v>286.34</v>
+        <v>12.33</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0</v>
+        <v>0.12</v>
       </c>
       <c r="CE2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>115</v>
+      </c>
+      <c r="CG2" t="s">
         <v>120</v>
       </c>
-      <c r="CF2" t="s">
-        <v>117</v>
-      </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>121</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>122</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO2" t="s">
         <v>123</v>
       </c>
-      <c r="CJ2" t="s">
+      <c r="CP2" t="s">
         <v>124</v>
       </c>
-      <c r="CO2" t="s">
-        <v>106</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>125</v>
-      </c>
       <c r="CQ2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="CT2" t="n">
         <v>0.0</v>
       </c>
-      <c r="CZ2" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3" t="s">
+        <v>107</v>
+      </c>
+      <c r="P3" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>109</v>
+      </c>
+      <c r="S3" t="s">
+        <v>110</v>
+      </c>
+      <c r="W3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH3" t="s">
         <v>126</v>
       </c>
-      <c r="DB2" t="s">
-        <v>108</v>
+      <c r="AN3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>118</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>2739.6</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>532.8</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>2739.6</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>18056.0</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>115</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>120</v>
+      </c>
+      <c r="CH3" t="s">
+        <v>121</v>
+      </c>
+      <c r="CI3" t="s">
+        <v>122</v>
+      </c>
+      <c r="CJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="CO3" t="s">
+        <v>123</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>129</v>
+      </c>
+      <c r="CQ3" t="s">
+        <v>115</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1647,13 +1811,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -1684,10 +1848,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -1717,13 +1881,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1757,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -1772,7 +1936,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -1830,64 +1994,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -1902,52 +2066,52 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -1999,76 +2163,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2102,19 +2266,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -2147,16 +2311,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2197,28 +2361,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -2248,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2">
@@ -2265,10 +2429,24 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D3" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -2293,8 +2471,8 @@
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="46.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="127.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="35.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="184.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2311,49 +2489,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
@@ -2361,19 +2539,28 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>117</v>
+      </c>
+      <c r="D2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" t="s">
+        <v>150</v>
       </c>
       <c r="F2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
-      </c>
-      <c r="M2" t="s">
-        <v>113</v>
+        <v>152</v>
+      </c>
+      <c r="H2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="3">
@@ -2381,28 +2568,28 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F3" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G3" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
@@ -2410,31 +2597,19 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M4" t="s">
         <v>112</v>
-      </c>
-      <c r="E4" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I4" t="s">
-        <v>158</v>
-      </c>
-      <c r="J4" t="s">
-        <v>159</v>
-      </c>
-      <c r="O4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="5">
@@ -2442,19 +2617,34 @@
         <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>154</v>
+      </c>
+      <c r="D5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5" t="s">
+        <v>161</v>
       </c>
       <c r="F5" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="G5" t="s">
-        <v>148</v>
-      </c>
-      <c r="M5" t="s">
-        <v>113</v>
+        <v>163</v>
+      </c>
+      <c r="I5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J5" t="s">
+        <v>165</v>
+      </c>
+      <c r="K5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="6">
@@ -2462,22 +2652,174 @@
         <v>104</v>
       </c>
       <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G7" t="s">
         <v>160</v>
       </c>
-      <c r="C6" t="s">
+      <c r="M7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" t="s">
+        <v>153</v>
+      </c>
+      <c r="J8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" t="s">
+        <v>170</v>
+      </c>
+      <c r="M9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" t="s">
         <v>161</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F10" t="s">
         <v>162</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G10" t="s">
         <v>163</v>
       </c>
-      <c r="F6" t="s">
+      <c r="I10" t="s">
         <v>164</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J10" t="s">
         <v>165</v>
+      </c>
+      <c r="K10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" t="s">
+        <v>170</v>
+      </c>
+      <c r="M12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H13" t="s">
+        <v>153</v>
+      </c>
+      <c r="J13" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2500,12 +2842,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -2537,13 +2879,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
@@ -2551,13 +2893,55 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2591,22 +2975,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2617,13 +3001,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -2634,13 +3018,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4">
@@ -2651,13 +3035,67 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C5" t="s">
         <v>175</v>
       </c>
-      <c r="D4" t="s">
-        <v>174</v>
-      </c>
-      <c r="E4" t="s">
-        <v>117</v>
+      <c r="D5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2693,28 +3131,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2">
@@ -2725,16 +3163,30 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F2" t="s">
-        <v>185</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2767,19 +3219,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2">
@@ -2790,13 +3242,30 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>191</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2830,22 +3299,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2887,61 +3356,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -2966,7 +3435,7 @@
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="64.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="62.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3028,58 +3497,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -3091,19 +3560,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -3118,25 +3587,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -3145,94 +3614,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
@@ -3243,40 +3712,43 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="G2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="J2" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K2" t="n">
-        <v>105.0</v>
+        <v>48.0</v>
       </c>
       <c r="L2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M2" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="T2" t="n">
-        <v>26.68</v>
+        <v>12.33</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
         <v>0.0</v>
@@ -3285,10 +3757,10 @@
         <v>0.0</v>
       </c>
       <c r="AB2" t="n">
-        <v>18031.0</v>
+        <v>18056.0</v>
       </c>
       <c r="AC2" t="n">
-        <v>799.05</v>
+        <v>365.28</v>
       </c>
       <c r="AF2" t="n">
         <v>0.0</v>
@@ -3302,76 +3774,70 @@
       <c r="AI2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>7.61</v>
-      </c>
       <c r="AK2" t="n">
         <v>0.0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0</v>
+        <v>365.28</v>
       </c>
       <c r="AN2" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS2" t="s">
-        <v>254</v>
-      </c>
       <c r="AY2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0</v>
       </c>
-      <c r="BO2" t="s">
-        <v>108</v>
-      </c>
       <c r="BR2" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="G3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="H3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I3" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="J3" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K3" t="n">
-        <v>468.0</v>
+        <v>360.0</v>
       </c>
       <c r="L3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M3" t="n">
         <v>33.0</v>
       </c>
       <c r="T3" t="n">
-        <v>116.49</v>
+        <v>93.34</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.69</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0</v>
@@ -3380,10 +3846,10 @@
         <v>0.0</v>
       </c>
       <c r="AB3" t="n">
-        <v>18031.0</v>
+        <v>18056.0</v>
       </c>
       <c r="AC3" t="n">
-        <v>3561.48</v>
+        <v>2739.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0.0</v>
@@ -3397,222 +3863,23 @@
       <c r="AI3" t="n">
         <v>0.0</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>7.61</v>
-      </c>
       <c r="AK3" t="n">
         <v>0.0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0</v>
+        <v>2739.6</v>
       </c>
       <c r="AN3" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS3" t="s">
-        <v>254</v>
-      </c>
       <c r="AY3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.0</v>
       </c>
-      <c r="BO3" t="s">
-        <v>108</v>
-      </c>
       <c r="BR3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F4" t="s">
-        <v>252</v>
-      </c>
-      <c r="G4" t="s">
-        <v>252</v>
-      </c>
-      <c r="H4" t="s">
-        <v>252</v>
-      </c>
-      <c r="I4" t="s">
-        <v>252</v>
-      </c>
-      <c r="J4" t="s">
-        <v>253</v>
-      </c>
-      <c r="K4" t="n">
-        <v>468.0</v>
-      </c>
-      <c r="L4" t="s">
-        <v>190</v>
-      </c>
-      <c r="M4" t="n">
-        <v>33.0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>116.49</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>18031.0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3561.48</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>254</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>255</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>108</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E5" t="s">
-        <v>258</v>
-      </c>
-      <c r="F5" t="s">
-        <v>252</v>
-      </c>
-      <c r="G5" t="s">
-        <v>252</v>
-      </c>
-      <c r="H5" t="s">
-        <v>252</v>
-      </c>
-      <c r="I5" t="s">
-        <v>252</v>
-      </c>
-      <c r="J5" t="s">
-        <v>253</v>
-      </c>
-      <c r="K5" t="n">
-        <v>105.0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>190</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>26.68</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>18031.0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>799.05</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>255</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>108</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3658,58 +3925,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
